--- a/data/trans_dic/P22$mutuaSPriv-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,5</t>
+          <t>0,93; 4,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,83</t>
+          <t>2,3; 7,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,21</t>
+          <t>0,39; 4,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,79</t>
+          <t>1,35; 5,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,31</t>
+          <t>0,37; 3,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,32</t>
+          <t>0,7; 4,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,27</t>
+          <t>0,32; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,33</t>
+          <t>1,86; 5,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,08</t>
+          <t>0,88; 3,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,24</t>
+          <t>1,96; 5,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,64; 2,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,69</t>
+          <t>1,94; 4,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,82</t>
+          <t>2,09; 5,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,55</t>
+          <t>1,81; 5,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,65</t>
+          <t>0,2; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,2</t>
+          <t>0,76; 3,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,02</t>
+          <t>1,8; 4,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,39</t>
+          <t>2,16; 6,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,48</t>
+          <t>0,55; 2,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,54</t>
+          <t>1,7; 4,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,96</t>
+          <t>2,38; 4,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,3</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,6</t>
+          <t>0,48; 1,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,25</t>
+          <t>1,44; 3,28</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,68</t>
+          <t>1,72; 5,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,02</t>
+          <t>0,88; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,71</t>
+          <t>0,28; 2,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,42</t>
+          <t>0,26; 2,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,14</t>
+          <t>0,39; 2,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,62</t>
+          <t>0,26; 1,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,26</t>
+          <t>1,17; 3,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,53</t>
+          <t>0,8; 2,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,34</t>
+          <t>0,78; 4,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,13</t>
+          <t>2,23; 7,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,16</t>
+          <t>0,83; 4,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,77</t>
+          <t>4,42; 12,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,61</t>
+          <t>1,04; 4,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,39</t>
+          <t>1,02; 4,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,59</t>
+          <t>0,99; 4,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,81</t>
+          <t>1,53; 4,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,3</t>
+          <t>1,19; 3,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,84</t>
+          <t>2,02; 4,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,29; 3,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,94</t>
+          <t>2,91; 6,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,42</t>
+          <t>5,35; 13,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,04</t>
+          <t>1,88; 8,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,68</t>
+          <t>0,72; 3,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,97</t>
+          <t>5,13; 12,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,15</t>
+          <t>0,9; 3,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,54</t>
+          <t>6,12; 11,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,38</t>
+          <t>1,16; 4,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,82</t>
+          <t>1,0; 2,8</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,32; 2,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,88</t>
+          <t>0,35; 3,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,33</t>
+          <t>0,66; 3,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,47</t>
+          <t>1,33; 4,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,03</t>
+          <t>0,34; 1,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,59</t>
+          <t>0,17; 1,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,1</t>
+          <t>1,23; 3,25</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,59</t>
+          <t>0,32; 2,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,64</t>
+          <t>0,7; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,05</t>
+          <t>1,91; 5,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,7</t>
+          <t>2,35; 6,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,76</t>
+          <t>0,28; 1,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,92</t>
+          <t>0,72; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,76</t>
+          <t>1,36; 3,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,12</t>
+          <t>1,35; 4,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,7</t>
+          <t>0,43; 1,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,3</t>
+          <t>0,92; 2,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,75</t>
+          <t>1,87; 3,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,96</t>
+          <t>2,2; 4,9</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,74</t>
+          <t>0,89; 2,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,44</t>
+          <t>0,97; 3,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,12</t>
+          <t>1,14; 3,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,68</t>
+          <t>0,57; 2,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,28</t>
+          <t>1,13; 3,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,56</t>
+          <t>1,24; 3,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,98</t>
+          <t>1,48; 3,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,31</t>
+          <t>0,89; 2,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,62</t>
+          <t>1,17; 2,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,05</t>
+          <t>1,38; 3,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,0</t>
+          <t>1,54; 3,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,16</t>
+          <t>0,9; 2,17</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,7</t>
+          <t>1,67; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,8</t>
+          <t>1,68; 2,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,71</t>
+          <t>1,58; 2,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,4</t>
+          <t>1,99; 3,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,61</t>
+          <t>1,59; 2,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,46</t>
+          <t>1,43; 2,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,29; 2,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,97</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,49</t>
+          <t>1,74; 2,45</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,47</t>
+          <t>1,69; 2,42</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,25</t>
+          <t>1,55; 2,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,98</t>
+          <t>2,12; 3,02</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2592; 12235</t>
+          <t>2526; 12867</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7276; 23064</t>
+          <t>6787; 23422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>977; 12380</t>
+          <t>1133; 12514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3983; 14928</t>
+          <t>4211; 16265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>960; 8637</t>
+          <t>970; 8811</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2074; 12403</t>
+          <t>2017; 12370</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1017; 9408</t>
+          <t>931; 9200</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5067; 18343</t>
+          <t>5393; 17269</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4489; 16388</t>
+          <t>4667; 16992</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11324; 30522</t>
+          <t>11414; 29851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3693; 16599</t>
+          <t>3703; 16707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12022; 28205</t>
+          <t>11687; 27935</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10741; 28695</t>
+          <t>10281; 29276</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9932; 27996</t>
+          <t>9146; 28565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1010; 8282</t>
+          <t>1011; 8472</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4019; 16597</t>
+          <t>3936; 16748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9130; 25304</t>
+          <t>9067; 24930</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12413; 33481</t>
+          <t>11312; 33174</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2068; 12952</t>
+          <t>2872; 13217</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8577; 23398</t>
+          <t>8750; 22588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23834; 49468</t>
+          <t>23731; 47632</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26184; 54546</t>
+          <t>25309; 55603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4906; 16364</t>
+          <t>4953; 17244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15259; 33584</t>
+          <t>14843; 33886</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5332</t>
+          <t>0; 5341</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5947</t>
+          <t>0; 6750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5412; 18002</t>
+          <t>5436; 18662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2797; 12697</t>
+          <t>2778; 12843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>919; 9086</t>
+          <t>930; 8921</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2058</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>892; 8127</t>
+          <t>883; 7369</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1292; 7459</t>
+          <t>1369; 7914</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1740; 10606</t>
+          <t>1677; 10219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6803</t>
+          <t>0; 6146</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7127; 21267</t>
+          <t>7622; 21554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5244; 16797</t>
+          <t>5307; 16816</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2756; 15481</t>
+          <t>2777; 15354</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8546; 26673</t>
+          <t>8343; 28261</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3082; 15377</t>
+          <t>3075; 15543</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13347; 36776</t>
+          <t>13805; 38881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2956; 13377</t>
+          <t>3870; 15196</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4824; 17070</t>
+          <t>3953; 16453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3952; 17778</t>
+          <t>3832; 17817</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7351; 22901</t>
+          <t>7277; 23495</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8397; 23960</t>
+          <t>8637; 26365</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16449; 36889</t>
+          <t>15427; 37962</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9016; 28587</t>
+          <t>9758; 28483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24481; 54726</t>
+          <t>22953; 53482</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10522; 27289</t>
+          <t>10870; 26499</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3603; 16978</t>
+          <t>3973; 17884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1466; 6584</t>
+          <t>1290; 6703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10880; 26928</t>
+          <t>10647; 26442</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6937</t>
+          <t>0; 6176</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5712</t>
+          <t>0; 5721</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1592; 6583</t>
+          <t>1884; 6614</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25210; 47444</t>
+          <t>25156; 46981</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7517</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4918; 18821</t>
+          <t>4973; 19991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3863; 10932</t>
+          <t>3892; 10855</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7474</t>
+          <t>862; 7913</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>968; 10630</t>
+          <t>969; 8934</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2139; 8974</t>
+          <t>1772; 8546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 7183</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3254; 11496</t>
+          <t>3424; 11185</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1880; 11169</t>
+          <t>1888; 10304</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>957; 8786</t>
+          <t>958; 9699</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6569; 16321</t>
+          <t>6499; 17133</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1970; 15927</t>
+          <t>1954; 14420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4777; 17508</t>
+          <t>4650; 16616</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12363; 33033</t>
+          <t>12504; 33561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14613; 41810</t>
+          <t>14696; 39664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1841; 11225</t>
+          <t>1791; 10514</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4884; 20256</t>
+          <t>4968; 21461</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8983; 25823</t>
+          <t>9350; 26390</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11645; 43445</t>
+          <t>11445; 41382</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5611; 21293</t>
+          <t>5436; 20187</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12282; 31163</t>
+          <t>12532; 31696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25407; 50218</t>
+          <t>25028; 51686</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30640; 73063</t>
+          <t>32451; 72160</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6345; 20302</t>
+          <t>6599; 19907</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7586; 26820</t>
+          <t>7535; 27128</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8474; 24263</t>
+          <t>8890; 25067</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5262; 24851</t>
+          <t>5249; 24963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8304; 25676</t>
+          <t>8835; 25514</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10261; 29297</t>
+          <t>10217; 30903</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13206; 32915</t>
+          <t>12268; 31583</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6265; 16550</t>
+          <t>6376; 16308</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16829; 39906</t>
+          <t>17872; 38196</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21908; 48818</t>
+          <t>22095; 51805</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24567; 48176</t>
+          <t>24754; 49885</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>13538; 35464</t>
+          <t>14750; 35666</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>54170; 88277</t>
+          <t>54737; 89218</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>58359; 95847</t>
+          <t>57480; 96884</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55232; 91957</t>
+          <t>53673; 88165</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71187; 117591</t>
+          <t>68990; 117270</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>54954; 88275</t>
+          <t>53667; 87804</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51711; 87500</t>
+          <t>50914; 89206</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46180; 77953</t>
+          <t>45600; 76957</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>68222; 108676</t>
+          <t>69581; 108980</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>117526; 165710</t>
+          <t>115980; 162688</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>117704; 172459</t>
+          <t>118191; 168854</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>106568; 155579</t>
+          <t>107698; 153993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>152145; 211974</t>
+          <t>150819; 215218</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutuaSPriv-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,73</t>
+          <t>0,94; 4,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,95</t>
+          <t>2,43; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,26</t>
+          <t>0,36; 4,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,22</t>
+          <t>1,56; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,38</t>
+          <t>0,37; 3,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,31</t>
+          <t>1,0; 4,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,2</t>
+          <t>0,32; 3,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,96</t>
+          <t>1,66; 5,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,19</t>
+          <t>0,9; 3,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,13</t>
+          <t>1,94; 5,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,87</t>
+          <t>0,67; 2,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,65</t>
+          <t>1,97; 4,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,94</t>
+          <t>2,15; 5,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,66</t>
+          <t>1,94; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,69</t>
+          <t>0,2; 1,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,23</t>
+          <t>0,78; 3,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,95</t>
+          <t>1,77; 4,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,33</t>
+          <t>2,33; 6,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,53</t>
+          <t>0,56; 2,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,39</t>
+          <t>1,5; 4,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,78</t>
+          <t>2,33; 4,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>2,57; 5,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,68</t>
+          <t>0,39; 1,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,28</t>
+          <t>1,35; 3,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,89</t>
+          <t>1,69; 5,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,06</t>
+          <t>0,77; 3,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,66</t>
+          <t>0,28; 2,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,27</t>
+          <t>0,38; 2,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,56</t>
+          <t>0,27; 1,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,3</t>
+          <t>1,1; 3,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,53</t>
+          <t>0,72; 2,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,31</t>
+          <t>0,77; 4,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,56</t>
+          <t>2,32; 6,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,2</t>
+          <t>0,82; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,44</t>
+          <t>4,1; 10,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,1</t>
+          <t>0,95; 4,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,23</t>
+          <t>1,07; 4,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,6</t>
+          <t>0,97; 4,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,94</t>
+          <t>2,1; 5,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,63</t>
+          <t>1,14; 3,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,98</t>
+          <t>2,14; 4,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,76</t>
+          <t>1,24; 3,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,78</t>
+          <t>3,37; 6,94</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,03</t>
+          <t>5,25; 12,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,47</t>
+          <t>1,62; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,75</t>
+          <t>0,95; 4,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 12,73</t>
+          <t>5,55; 13,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,17</t>
+          <t>0,75; 2,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,43</t>
+          <t>6,16; 11,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,65</t>
+          <t>1,17; 4,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,8</t>
+          <t>1,06; 2,98</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,92</t>
+          <t>0,32; 2,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,26</t>
+          <t>0,35; 3,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,17</t>
+          <t>0,65; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,35</t>
+          <t>1,23; 4,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,88</t>
+          <t>0,35; 2,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,75</t>
+          <t>0,17; 1,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,25</t>
+          <t>1,21; 3,25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,35</t>
+          <t>0,37; 2,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,51</t>
+          <t>0,7; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,14</t>
+          <t>1,87; 4,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,35</t>
+          <t>2,69; 6,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,65</t>
+          <t>0,29; 1,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,09</t>
+          <t>0,7; 2,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,84</t>
+          <t>1,4; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,87</t>
+          <t>2,7; 5,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,61</t>
+          <t>0,45; 1,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,34</t>
+          <t>0,91; 2,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,86</t>
+          <t>1,92; 3,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,9</t>
+          <t>2,92; 5,5</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,68</t>
+          <t>0,93; 2,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,48</t>
+          <t>0,95; 3,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,22</t>
+          <t>1,16; 3,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,69</t>
+          <t>1,18; 3,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,26</t>
+          <t>1,09; 3,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,75</t>
+          <t>1,23; 3,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,82</t>
+          <t>1,52; 3,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,28</t>
+          <t>0,91; 2,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,5</t>
+          <t>1,18; 2,67</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,23</t>
+          <t>1,37; 2,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,11</t>
+          <t>1,5; 3,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,17</t>
+          <t>1,19; 2,43</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,73</t>
+          <t>1,68; 2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,83</t>
+          <t>1,71; 2,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,6</t>
+          <t>1,58; 2,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,39</t>
+          <t>2,33; 3,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,6</t>
+          <t>1,69; 2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,51</t>
+          <t>1,44; 2,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,17</t>
+          <t>1,28; 2,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>2,13; 3,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,45</t>
+          <t>1,78; 2,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,42</t>
+          <t>1,72; 2,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,22</t>
+          <t>1,52; 2,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,02</t>
+          <t>2,35; 3,17</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>18669</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2526; 12867</t>
+          <t>2551; 12853</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6787; 23422</t>
+          <t>7167; 22024</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1133; 12514</t>
+          <t>1053; 11860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4211; 16265</t>
+          <t>4973; 16210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>970; 8811</t>
+          <t>964; 8347</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2017; 12370</t>
+          <t>2859; 12342</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>931; 9200</t>
+          <t>927; 9780</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5393; 17269</t>
+          <t>5247; 17834</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4667; 16992</t>
+          <t>4811; 17888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11414; 29851</t>
+          <t>11290; 30020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3703; 16707</t>
+          <t>3883; 16627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11687; 27935</t>
+          <t>12523; 27282</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>23079</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10281; 29276</t>
+          <t>10600; 28051</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9146; 28565</t>
+          <t>9812; 29003</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1011; 8472</t>
+          <t>1012; 8294</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3936; 16748</t>
+          <t>4120; 17716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9067; 24930</t>
+          <t>8913; 24738</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11312; 33174</t>
+          <t>12229; 32954</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2872; 13217</t>
+          <t>2930; 13083</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8750; 22588</t>
+          <t>8212; 22395</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23731; 47632</t>
+          <t>23189; 46477</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25309; 55603</t>
+          <t>26478; 55852</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4953; 17244</t>
+          <t>3996; 16263</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14843; 33886</t>
+          <t>14517; 33482</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9648</t>
         </is>
       </c>
     </row>
@@ -2625,27 +2625,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 6087</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6750</t>
+          <t>0; 6184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5436; 18662</t>
+          <t>5362; 18033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2778; 12843</t>
+          <t>2447; 11859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>930; 8921</t>
+          <t>929; 8279</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,32 +2655,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>883; 7369</t>
+          <t>879; 7354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1369; 7914</t>
+          <t>1359; 7874</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1677; 10219</t>
+          <t>1788; 10205</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6146</t>
+          <t>0; 6878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7622; 21554</t>
+          <t>7191; 21134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5307; 16816</t>
+          <t>4823; 16162</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>38629</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2777; 15354</t>
+          <t>2759; 15166</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8343; 28261</t>
+          <t>8686; 25629</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3075; 15543</t>
+          <t>3047; 16534</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13805; 38881</t>
+          <t>15280; 40308</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3870; 15196</t>
+          <t>3538; 14959</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3953; 16453</t>
+          <t>4180; 16727</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3832; 17817</t>
+          <t>3747; 18296</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7277; 23495</t>
+          <t>8846; 22102</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8637; 26365</t>
+          <t>8306; 23759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15427; 37962</t>
+          <t>16290; 38042</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9758; 28483</t>
+          <t>9409; 27192</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22953; 53482</t>
+          <t>26773; 55150</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>8009</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10870; 26499</t>
+          <t>10665; 26196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3973; 17884</t>
+          <t>3429; 16280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1290; 6703</t>
+          <t>1949; 9025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10647; 26442</t>
+          <t>11526; 27228</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 7258</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5721</t>
+          <t>0; 6647</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1884; 6614</t>
+          <t>1711; 6712</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25156; 46981</t>
+          <t>25319; 47590</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 6324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4973; 19991</t>
+          <t>5010; 19213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3892; 10855</t>
+          <t>4589; 12913</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10592</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>862; 7913</t>
+          <t>858; 7315</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>969; 8934</t>
+          <t>967; 9157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1772; 8546</t>
+          <t>1751; 8244</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7183</t>
+          <t>0; 7149</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3424; 11185</t>
+          <t>3249; 11512</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1888; 10304</t>
+          <t>1898; 11045</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>958; 9699</t>
+          <t>967; 10669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6499; 17133</t>
+          <t>6452; 17370</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>30387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>60820</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1954; 14420</t>
+          <t>2276; 16060</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4650; 16616</t>
+          <t>4649; 15534</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12504; 33561</t>
+          <t>12215; 32198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14696; 39664</t>
+          <t>19331; 49495</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1791; 10514</t>
+          <t>1835; 11257</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4968; 21461</t>
+          <t>4889; 20023</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9350; 26390</t>
+          <t>9641; 25978</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11445; 41382</t>
+          <t>20802; 45055</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5436; 20187</t>
+          <t>5575; 21530</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12532; 31696</t>
+          <t>12411; 30370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25028; 51686</t>
+          <t>25664; 51007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32451; 72160</t>
+          <t>43595; 82001</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>28025</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6599; 19907</t>
+          <t>6878; 20173</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7535; 27128</t>
+          <t>7376; 26689</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8890; 25067</t>
+          <t>9066; 25021</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5249; 24963</t>
+          <t>9437; 26304</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8835; 25514</t>
+          <t>8513; 25126</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10217; 30903</t>
+          <t>10140; 30123</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12268; 31583</t>
+          <t>12571; 32228</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6376; 16308</t>
+          <t>7539; 19735</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17872; 38196</t>
+          <t>17949; 40656</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22095; 51805</t>
+          <t>21960; 47875</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24754; 49885</t>
+          <t>24017; 50194</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>14750; 35666</t>
+          <t>19449; 39538</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>103212</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>181220</t>
+          <t>197473</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>54737; 89218</t>
+          <t>55000; 88610</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>57480; 96884</t>
+          <t>58453; 97014</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53673; 88165</t>
+          <t>53681; 88495</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68990; 117270</t>
+          <t>82163; 130113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>53667; 87804</t>
+          <t>57167; 90229</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50914; 89206</t>
+          <t>51335; 87605</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45600; 76957</t>
+          <t>45226; 76426</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>69581; 108980</t>
+          <t>79386; 113514</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>115980; 162688</t>
+          <t>118130; 166093</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118191; 168854</t>
+          <t>120082; 169987</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>107698; 153993</t>
+          <t>105444; 153728</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>150819; 215218</t>
+          <t>170832; 230548</t>
         </is>
       </c>
     </row>
